--- a/data/vann-nett_data.xlsx
+++ b/data/vann-nett_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.0133</v>
+        <v>0.0182</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0426</v>
+        <v>0.0582</v>
       </c>
       <c r="H9" t="n">
-        <v>750</v>
+        <v>548</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
@@ -995,7 +995,7 @@
         <v>2026</v>
       </c>
       <c r="N9" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1035,13 +1035,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.2492</v>
+        <v>0.2776</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4045</v>
+        <v>0.4371</v>
       </c>
       <c r="H10" t="n">
-        <v>1304.204932</v>
+        <v>1170.623534</v>
       </c>
       <c r="I10" t="n">
         <v>325</v>
@@ -1063,7 +1063,7 @@
         <v>2026</v>
       </c>
       <c r="N10" t="n">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>6.89</v>
+        <v>6.843809</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
@@ -1121,7 +1121,7 @@
         <v>2026</v>
       </c>
       <c r="N11" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>0.5</v>
       </c>
       <c r="H12" t="n">
-        <v>24</v>
+        <v>17.6</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
@@ -1181,7 +1181,7 @@
         <v>2020</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>0.5</v>
       </c>
       <c r="H13" t="n">
-        <v>45.919601</v>
+        <v>42.24225</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
@@ -1241,7 +1241,7 @@
         <v>2026</v>
       </c>
       <c r="N13" t="n">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>13.330612</v>
+        <v>11.390909</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
@@ -1299,7 +1299,7 @@
         <v>2025</v>
       </c>
       <c r="N14" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0.2474</v>
+        <v>0.2457</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4024</v>
+        <v>0.4005</v>
       </c>
       <c r="H44" t="n">
-        <v>1313.451612</v>
+        <v>1322.784</v>
       </c>
       <c r="I44" t="n">
         <v>325</v>
@@ -3147,7 +3147,7 @@
         <v>2026</v>
       </c>
       <c r="N44" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>34.871028</v>
+        <v>35.586138</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
@@ -3205,7 +3205,7 @@
         <v>2025</v>
       </c>
       <c r="N45" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>13.990163</v>
+        <v>14.001626</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
@@ -3263,7 +3263,7 @@
         <v>2026</v>
       </c>
       <c r="N46" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>0.5</v>
       </c>
       <c r="H49" t="n">
-        <v>64.364</v>
+        <v>63.670634</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
@@ -3437,7 +3437,7 @@
         <v>2026</v>
       </c>
       <c r="N49" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>34.871028</v>
+        <v>35.586138</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
@@ -3495,7 +3495,7 @@
         <v>2025</v>
       </c>
       <c r="N50" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3601,13 +3601,13 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.3663</v>
+        <v>0.3537</v>
       </c>
       <c r="G52" t="n">
-        <v>0.539</v>
+        <v>0.5245</v>
       </c>
       <c r="H52" t="n">
-        <v>887.260869</v>
+        <v>918.782608</v>
       </c>
       <c r="I52" t="n">
         <v>325</v>
@@ -3626,7 +3626,7 @@
         <v>2020</v>
       </c>
       <c r="M52" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
@@ -3671,7 +3671,7 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>29.797297</v>
+        <v>29.9</v>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
@@ -3687,7 +3687,7 @@
         <v>2025</v>
       </c>
       <c r="N53" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>15.272727</v>
+        <v>15.318181</v>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
@@ -3742,7 +3742,7 @@
         <v>2020</v>
       </c>
       <c r="M54" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="N54" t="n">
         <v>44</v>
@@ -3905,7 +3905,7 @@
         <v>0.5</v>
       </c>
       <c r="H57" t="n">
-        <v>60.234042</v>
+        <v>59.765957</v>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
@@ -3918,7 +3918,7 @@
         <v>2020</v>
       </c>
       <c r="M57" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="N57" t="n">
         <v>47</v>
@@ -3963,7 +3963,7 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>29.797297</v>
+        <v>29.9</v>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
@@ -3979,7 +3979,7 @@
         <v>2025</v>
       </c>
       <c r="N58" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>002-3655-R</t>
+          <t>002-3692-R</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4015,31 +4015,21 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.5513</v>
-      </c>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>861.961038</v>
-      </c>
-      <c r="I59" t="n">
-        <v>325</v>
-      </c>
+        <v>1400.282608</v>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>µg/l</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>550.0;775.0;1325.0;2025.0</t>
-        </is>
-      </c>
+          <t>µg/l N</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
         <v>2020</v>
       </c>
@@ -4047,7 +4037,7 @@
         <v>2026</v>
       </c>
       <c r="N59" t="n">
-        <v>154</v>
+        <v>46</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4063,7 +4053,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>002-3655-R</t>
+          <t>002-3692-R</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4078,7 +4068,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Phosphate</t>
+          <t>Total organic carbon</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4089,12 +4079,12 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>17.5288</v>
+        <v>11.779545</v>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>µg/l</t>
+          <t>mg/l C</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4102,10 +4092,10 @@
         <v>2020</v>
       </c>
       <c r="M60" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="N60" t="n">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4121,7 +4111,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>002-3655-R</t>
+          <t>002-3692-R</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4131,12 +4121,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>QE3-1-6-1 - Nitrogen conditions</t>
+          <t>QE3-1-6-2 - Phosphorus Conditions</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Total organic carbon</t>
+          <t>Orthophosphate</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4147,23 +4137,23 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>12.721333</v>
+        <v>21</v>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>mg/l C</t>
+          <t>µg/l P</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="M61" t="n">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="N61" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4179,7 +4169,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>002-3655-R</t>
+          <t>002-3692-R</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,12 +4179,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>QE3-1-6-1 - Nitrogen conditions</t>
+          <t>QE3-1-6-2 - Phosphorus Conditions</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Total oxidised Nitrogen</t>
+          <t>Total phosphorous</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4205,23 +4195,23 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>30</v>
+        <v>52.761702</v>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>µg/l</t>
+          <t>µg/l P</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="M62" t="n">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4237,7 +4227,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>002-3655-R</t>
+          <t>002-3692-R</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4252,7 +4242,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Orthophosphate</t>
+          <t>Phosphate</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4263,23 +4253,23 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>15.63238</v>
+        <v>30.508571</v>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>µg/l</t>
+          <t>µg/l P</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="M63" t="n">
         <v>2025</v>
       </c>
       <c r="N63" t="n">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4305,12 +4295,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>QE3-1-6-2 - Phosphorus Conditions</t>
+          <t>QE3-1-6-1 - Nitrogen conditions</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Total phosphorous</t>
+          <t>Total nitrogen</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4319,16 +4309,16 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.3241</v>
+        <v>0.377</v>
       </c>
       <c r="G64" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.5513</v>
       </c>
       <c r="H64" t="n">
-        <v>33.944516</v>
+        <v>861.961038</v>
       </c>
       <c r="I64" t="n">
-        <v>11</v>
+        <v>325</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4337,7 +4327,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>20.0;29.0;58.0;98.0</t>
+          <t>550.0;775.0;1325.0;2025.0</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -4347,7 +4337,7 @@
         <v>2026</v>
       </c>
       <c r="N64" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4373,7 +4363,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>QE3-1-6-2 - Phosphorus Conditions</t>
+          <t>QE3-1-6-1 - Nitrogen conditions</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4418,6 +4408,306 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>002-3655-R</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PhysicoChemical</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>QE3-1-6-1 - Nitrogen conditions</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Total organic carbon</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="n">
+        <v>12.721333</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>mg/l C</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>2020</v>
+      </c>
+      <c r="M66" t="n">
+        <v>2026</v>
+      </c>
+      <c r="N66" t="n">
+        <v>150</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Vannmiljø</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>002-3655-R</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PhysicoChemical</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>QE3-1-6-1 - Nitrogen conditions</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Total oxidised Nitrogen</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>µg/l</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="n">
+        <v>2019</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2019</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Vannmiljø</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>002-3655-R</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PhysicoChemical</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>QE3-1-6-2 - Phosphorus Conditions</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Orthophosphate</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="n">
+        <v>15.63238</v>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>µg/l</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>2021</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2025</v>
+      </c>
+      <c r="N68" t="n">
+        <v>105</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Vannmiljø</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>002-3655-R</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PhysicoChemical</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>QE3-1-6-2 - Phosphorus Conditions</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Total phosphorous</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.5417999999999999</v>
+      </c>
+      <c r="H69" t="n">
+        <v>33.944516</v>
+      </c>
+      <c r="I69" t="n">
+        <v>11</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>µg/l</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>20.0;29.0;58.0;98.0</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>2020</v>
+      </c>
+      <c r="M69" t="n">
+        <v>2026</v>
+      </c>
+      <c r="N69" t="n">
+        <v>155</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Vannmiljø</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>002-3655-R</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PhysicoChemical</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>QE3-1-6-2 - Phosphorus Conditions</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Phosphate</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="n">
+        <v>17.5288</v>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>µg/l</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="n">
+        <v>2020</v>
+      </c>
+      <c r="M70" t="n">
+        <v>2025</v>
+      </c>
+      <c r="N70" t="n">
+        <v>125</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Vannmiljø</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
